--- a/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
+++ b/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K16" s="67" t="inlineStr">
         <is>
-          <t>Hito H3. Los dos agentes ya arrancan aislados con herramientas/robot.sh, cada uno con su dominio ROS y su GAZEBO_MASTER_URI. Falta la corrida con una meta por agente: siguen abiertos dos defectos que bloquean OE4 —una lectura de /odom reportó el desplazamiento del otro robot, y desvío de hasta 18° con angular.z = 0</t>
+          <t>Hito H3. Los dos agentes ya arrancan aislados con herramientas/robot.sh, cada uno con su dominio ROS y su GAZEBO_MASTER_URI, y cada uno navega sobre el mapa de su nivel: robot1 el 2026-08-21 y robot2 el 2026-08-24. Falta la corrida con los dos a la vez, que es la condición del hito. Sigue abierto el defecto que la bloquea y que contaminaría OE4: una lectura de /odom reportó el desplazamiento del otro robot, y esa lectura apareció justamente con dos agentes corriendo en simultáneo. El desvío de hasta 18° con angular.z = 0 quedó resuelto el 2026-08-18: era el mismo defecto de conversión de angular.z y no una causa aparte</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="E17" s="75" t="inlineStr">
         <is>
-          <t>mundo_definitivo_piso1.yaml verificado; falta el par del piso 2</t>
+          <t>maps/mundo_definitivo_piso1.yaml y maps/mundo_definitivo_piso2.yaml, los dos verificados con herramientas/verificar_mapa.py; herramientas/buscar_vanos.py</t>
         </is>
       </c>
       <c r="F17" s="74" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="J17" s="77" t="inlineStr">
         <is>
-          <t>En ejecución</t>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K17" s="75" t="inlineStr">
         <is>
-          <t>Piso 1 hecho el 2026-08-20: el mapa se deriva de la geometría del .world y no de SLAM, con 0 de 4725 obstáculos sin pared real detrás. Falta el mapa del piso 2 y la pila Nav2 del segundo agente</t>
+          <t>Piso 1 el 2026-08-20 y piso 2 el 2026-08-23: el mapa se deriva de la geometría del .world y no de SLAM. El 2026-08-24 se rehicieron los dos. Los mapas anteriores se acotaban con opciones --region, que recortan el resultado ya calculado y dejan el mundo abierto: el mapa salía bien pero Gazebo y el LiDAR seguían viendo los huecos. Se sellaron los dos mundos con paneles sintéticos Limite_* —7 en el piso 1 y 23 en el piso 2— ubicados analíticamente con herramientas/buscar_vanos.py, y los mapas se regeneraron sin una sola región. Verificación: 0 de 7977 obstáculos sin pared real detrás y 0 celdas de frontera libre↔desconocido de 40 573 en el piso 2. La pila Nav2 por agente queda en herramientas/robot.sh, con el mapa de cada piso pasado de forma explícita; robot2 navegó sobre el suyo el 2026-08-24 con 0,190 m de error contra /odom</t>
         </is>
       </c>
     </row>
@@ -8010,9 +8010,9 @@
   </sheetData>
   <mergeCells count="44">
     <mergeCell ref="B45:X45"/>
-    <mergeCell ref="B37:T37"/>
     <mergeCell ref="B63:X63"/>
     <mergeCell ref="B41:X41"/>
+    <mergeCell ref="B37:T37"/>
     <mergeCell ref="B50:X50"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="A29:A31"/>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="D3" s="75" t="inlineStr">
         <is>
-          <t>Rama «integracion-nav2» y Documentos/DESARROLLO_NAV2.md · maps/mundo_definitivo_piso1.yaml · Documentos/Evidencia/S19_spike_p1_p2_hardware.md · herramientas/verificar_lidar.py · rosbags de /scan, /odom y /cmd_vel del vehículo real · registro audiovisual de la locomoción · lista de verificación de paridad entre vehículos</t>
+          <t>Rama «integracion-nav2» y Documentos/DESARROLLO_NAV2.md · maps/mundo_definitivo_piso1.yaml y maps/mundo_definitivo_piso2.yaml · herramientas/buscar_vanos.py · Documentos/Evidencia/S19_spike_p1_p2_hardware.md · herramientas/verificar_lidar.py · rosbags de /scan, /odom y /cmd_vel del vehículo real · registro audiovisual de la locomoción · lista de verificación de paridad entre vehículos</t>
         </is>
       </c>
       <c r="E3" s="75" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="F3" s="75" t="inlineStr">
         <is>
-          <t>50 %. En simulación: un agente navega de forma autónoma con Nav2 + AMCL sobre un mapa derivado de la geometría del mundo, con deriva de 0,045 m frente a la odometría, opera bajo espacio de nombres y el 2026-08-21 alcanza los tres destinos probados sobre el entorno definitivo. En hardware (spike de S19): el LiDAR real repite la misma pared con 2,8 mm de dispersión; el LiDAR de fábrica del kit —un RPLIDAR A1M8-R5— publica /scan con 360 muestras sobre 360° a 6,80 Hz; y el vehículo se comanda desde ROS 2 sin la interfaz web, con dirección y tracción proporcionales. Falta cerrar la cadena /cmd_vel → servo, que el LiDAR conviva con la pila del vehículo —el lanzador pide rplidar_node y el ejecutable instalado se llama rplidar_composition— y la comunicación entre agentes.</t>
+          <t>55 %. En simulación: un agente navega de forma autónoma con Nav2 + AMCL sobre un mapa derivado de la geometría del mundo, con deriva de 0,045 m frente a la odometría, opera bajo espacio de nombres y el 2026-08-21 alcanza los tres destinos probados sobre el entorno definitivo. Los dos niveles tienen ya mundo y mapa propios, sellados con paneles sintéticos y verificados sin recortes (2026-08-24), y el segundo agente navega sobre el suyo con 0,190 m de error frente a la odometría. En hardware (spike de S19): el LiDAR real repite la misma pared con 2,8 mm de dispersión; el LiDAR de fábrica del kit —un RPLIDAR A1M8-R5— publica /scan con 360 muestras sobre 360° a 6,80 Hz; y el vehículo se comanda desde ROS 2 sin la interfaz web, con dirección y tracción proporcionales. Falta cerrar la cadena /cmd_vel → servo, que el LiDAR conviva con la pila del vehículo —el lanzador pide rplidar_node y el ejecutable instalado se llama rplidar_composition— y la comunicación entre agentes.</t>
         </is>
       </c>
     </row>

--- a/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
+++ b/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E16" s="67" t="inlineStr">
         <is>
-          <t>Registro audiovisual y salida de «ros2 node list»; Documentos/Evidencia/S19_dos_agentes.md</t>
+          <t>Documentos/Evidencia/S20_hito_h3_dos_agentes.md, con los dos rosbag2 (/robot1 y /robot2) medidos contra /odom por herramientas/analizar_maniobra.py</t>
         </is>
       </c>
       <c r="F16" s="72" t="inlineStr">
@@ -2362,14 +2362,14 @@
           <t>Réplica del laboratorio en SDF (act. 12) y contrato de interfaces verificado</t>
         </is>
       </c>
-      <c r="J16" s="77" t="inlineStr">
-        <is>
-          <t>En ejecución</t>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K16" s="67" t="inlineStr">
         <is>
-          <t>Hito H3. Los dos agentes ya arrancan aislados con herramientas/robot.sh, cada uno con su dominio ROS y su GAZEBO_MASTER_URI, y cada uno navega sobre el mapa de su nivel: robot1 el 2026-08-21 y robot2 el 2026-08-24. Falta la corrida con los dos a la vez, que es la condición del hito. Sigue abierto el defecto que la bloquea y que contaminaría OE4: una lectura de /odom reportó el desplazamiento del otro robot, y esa lectura apareció justamente con dos agentes corriendo en simultáneo. El desvío de hasta 18° con angular.z = 0 quedó resuelto el 2026-08-18: era el mismo defecto de conversión de angular.z y no una causa aparte</t>
+          <t>Hito H3 cerrado el 2026-08-25: los dos agentes navegaron a la vez, cada uno en su piso, hasta su punto de transferencia. Error real de llegada contra /odom: 0,281 m en robot1 y 0,143 m en robot2. El control es robot2 solo el 2026-08-24, que dio 0,190 m: con un agente en el otro dominio no empeora. El defecto que bloqueaba el hito queda cerrado con causa y no por no reproducirse: los tópicos no se ven entre dominios DDS, así que el /odom cruzado venía del demonio de ros2cli y no de la publicación bajo espacio de nombres; la mitigación pasa de --no-daemon a matar el demonio. Quedan tres defectos nuevos anotados en la evidencia: el vehículo sale de la tolerancia estando quieto (93 s sin una sola orden y 4,0 cm recorridos), AMCL se sobreconfía en la aproximación de frente a la escalera del piso 2, y la activación de los siete controladores compite consigo misma al arrancar seis en paralelo</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2580,12 @@
       </c>
       <c r="J20" s="77" t="inlineStr">
         <is>
-          <t>En ejecución</t>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K20" s="67" t="inlineStr">
         <is>
-          <t>Se escribe ANTES de instrumentar, no después. Su dependencia bloqueante quedó resuelta el 2026-08-20: puntos_interes.yaml define 15 destinos del piso 1, de donde salen los orígenes y destinos de las 30 repeticiones. Falta redactar PROTOCOLO_EXPERIMENTAL.md</t>
+          <t>Se escribe ANTES de instrumentar, no después. Un protocolo redactado después de ver los resultados se acomoda sin querer a lo que salió, y la campaña deja de poder refutar nada: la fecha del archivo en el historial de git es parte de la evidencia. Su dependencia bloqueante quedó resuelta el 2026-08-20, cuando puntos_interes.yaml definió los 15 destinos del piso 1, de donde salen los orígenes y destinos de las 30 repeticiones. Documentos/PROTOCOLO_EXPERIMENTAL.md quedó redactado el 2026-08-22 y es la condición 3 de cierre de S19. Fija además que el éxito se mide contra /odom y no contra el SUCCEEDED de Nav2, tras la corrida del 2026-08-21 en que Nav2 devolvió SUCCEEDED a 0,296 m del destino, por encima de la tolerancia configurada de 0,25 m. Lo que queda de OE4 no es este documento sino la instrumentación, que se construye junto con la coordinación (act. 22) y el relevo (act. 26)</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="F3" s="75" t="inlineStr">
         <is>
-          <t>55 %. En simulación: un agente navega de forma autónoma con Nav2 + AMCL sobre un mapa derivado de la geometría del mundo, con deriva de 0,045 m frente a la odometría, opera bajo espacio de nombres y el 2026-08-21 alcanza los tres destinos probados sobre el entorno definitivo. Los dos niveles tienen ya mundo y mapa propios, sellados con paneles sintéticos y verificados sin recortes (2026-08-24), y el segundo agente navega sobre el suyo con 0,190 m de error frente a la odometría. En hardware (spike de S19): el LiDAR real repite la misma pared con 2,8 mm de dispersión; el LiDAR de fábrica del kit —un RPLIDAR A1M8-R5— publica /scan con 360 muestras sobre 360° a 6,80 Hz; y el vehículo se comanda desde ROS 2 sin la interfaz web, con dirección y tracción proporcionales. Falta cerrar la cadena /cmd_vel → servo, que el LiDAR conviva con la pila del vehículo —el lanzador pide rplidar_node y el ejecutable instalado se llama rplidar_composition— y la comunicación entre agentes.</t>
+          <t>55 %. En simulación: un agente navega de forma autónoma con Nav2 + AMCL sobre un mapa derivado de la geometría del mundo, con deriva de 0,045 m frente a la odometría, opera bajo espacio de nombres y el 2026-08-21 alcanza los tres destinos probados sobre el entorno definitivo. Los dos niveles tienen ya mundo y mapa propios, sellados con paneles sintéticos y verificados sin recortes (2026-08-24), y el segundo agente navega sobre el suyo con 0,190 m de error frente a la odometría. El 2026-08-25 los dos navegaron a la vez, cada uno en su piso, hasta su punto de transferencia: 0,281 m y 0,143 m frente a la odometría, sin que la simultaneidad degradara al segundo agente. En hardware (spike de S19): el LiDAR real repite la misma pared con 2,8 mm de dispersión; el LiDAR de fábrica del kit —un RPLIDAR A1M8-R5— publica /scan con 360 muestras sobre 360° a 6,80 Hz; y el vehículo se comanda desde ROS 2 sin la interfaz web, con dirección y tracción proporcionales. Falta cerrar la cadena /cmd_vel → servo, que el LiDAR conviva con la pila del vehículo —el lanzador pide rplidar_node y el ejecutable instalado se llama rplidar_composition— y la comunicación entre agentes.</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="F5" s="75" t="inlineStr">
         <is>
-          <t>0 %. No existe instrumentación ni protocolo experimental. La dependencia que lo bloqueaba quedó resuelta el 2026-08-20: puntos_interes.yaml define las 15 localizaciones de interés del piso 1, de donde salen los orígenes y destinos de las 30 repeticiones. El protocolo se escribe en S19 y la instrumentación se construye junto con la coordinación (S20) y el relevo (S21), no al final, para que las campañas de S24 y S25 solo tengan que ejecutarse.</t>
+          <t>10 %. El protocolo experimental está escrito y versionado desde el 2026-08-22 (Documentos/PROTOCOLO_EXPERIMENTAL.md, act. 19 de las diez que componen este objetivo): fija las cuatro métricas, N = 30, los criterios de éxito, el tratamiento de la corrida fallida y el formato de registro, y establece que el éxito se mide contra /odom y no contra el SUCCEEDED de Nav2. Su dependencia quedó resuelta el 2026-08-20: puntos_interes.yaml define las localizaciones de interés de donde salen los orígenes y destinos. NO existe todavía instrumentación, ni una sola corrida registrada, ni conjunto de datos: por eso el avance es del 10 % y no más. La instrumentación se construye junto con la coordinación (S20) y el relevo (S21), no al final, para que las campañas de S24 y S25 solo tengan que ejecutarse. Defecto abierto que hoy sesgaría la tasa de éxito: R12, el verificador de meta cuenta como fallo llegadas que fueron buenas</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E4" s="67" t="inlineStr">
         <is>
-          <t>Registro audiovisual y mapas de los dos niveles</t>
+          <t>Los dos rosbag2 de la corrida simultánea y su medición contra /odom, más los mapas de los dos niveles: Documentos/Evidencia/S20_hito_h3_dos_agentes.md</t>
         </is>
       </c>
       <c r="F4" s="67" t="inlineStr">
@@ -8479,9 +8479,9 @@
           <t>Nodo de coordinación</t>
         </is>
       </c>
-      <c r="H4" s="77" t="inlineStr">
-        <is>
-          <t>En ejecución</t>
+      <c r="H4" s="76" t="inlineStr">
+        <is>
+          <t>Finalizada</t>
         </is>
       </c>
     </row>

--- a/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
+++ b/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C23"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="62" min="1" max="1"/>
@@ -1261,6 +1261,7 @@
     <col width="96" customWidth="1" style="62" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="15" customHeight="1" s="63">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -1275,6 +1276,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="63">
       <c r="B5" s="66" t="inlineStr">
         <is>
@@ -1355,7 +1357,7 @@
       </c>
       <c r="C11" s="67" t="inlineStr">
         <is>
-          <t>21 de agosto de 2026</t>
+          <t>27 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1423,6 +1425,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="63">
       <c r="B18" s="68" t="inlineStr">
         <is>
@@ -1430,6 +1433,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="25.5" customHeight="1" s="63">
       <c r="B20" s="69" t="inlineStr">
         <is>
@@ -2686,12 +2690,12 @@
       </c>
       <c r="J22" s="78" t="inlineStr">
         <is>
-          <t>Reprogramada</t>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K22" s="67" t="inlineStr">
         <is>
-          <t>Integración de los módulos: Cap. 8 la situaba en S16–S18; se traslada a S18–S22. Hito H4</t>
+          <t>Integración de los módulos: Cap. 8 la situaba en S16–S18; se corre a S18–S22. Finalizada el 2026-08-24: paquete «coordinacion» con el relevo escrito como función pura y las 992 combinaciones origen–destino del catálogo real verificadas sin simulador. El nodo verifica cada llegada contra /odom y no contra el SUCCEEDED de Nav2. Pendiente de probar con destino en el nivel 2: robot1 y robot2 corren en dominios DDS distintos y un nodo de ROS 2 vive en uno solo, así que el coordinador no alcanza a los dos.</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2720,7 @@
       </c>
       <c r="E23" s="75" t="inlineStr">
         <is>
-          <t>Archivo CSV de eventos con las columnas de las dos métricas</t>
+          <t>Registro JSON por misión validado contra el esquema versionado de RF-25, con las marcas de tiempo de respuesta y de asignación</t>
         </is>
       </c>
       <c r="F23" s="74" t="inlineStr">
@@ -2741,10 +2745,14 @@
       </c>
       <c r="J23" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K23" s="75" t="n"/>
+          <t>Finalizada</t>
+        </is>
+      </c>
+      <c r="K23" s="75" t="inlineStr">
+        <is>
+          <t>Finalizada el 2026-08-27. Desviación declarada frente al producto previsto: el registro es un archivo JSON por misión validado contra esquema, no un CSV de eventos; el CSV se reconstruye del conjunto y el esquema permite comprobar cada campo, cosa que un CSV no. Verificado sobre dos misiones completas de dos tramos (S20_rutas_03 y S20_rutas_04). Todas las marcas salen de /clock, como exige el §3 del protocolo experimental.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="63">
       <c r="A24" s="72" t="n">
@@ -8279,7 +8287,7 @@
       </c>
       <c r="F5" s="75" t="inlineStr">
         <is>
-          <t>10 %. El protocolo experimental está escrito y versionado desde el 2026-08-22 (Documentos/PROTOCOLO_EXPERIMENTAL.md, act. 19 de las diez que componen este objetivo): fija las cuatro métricas, N = 30, los criterios de éxito, el tratamiento de la corrida fallida y el formato de registro, y establece que el éxito se mide contra /odom y no contra el SUCCEEDED de Nav2. Su dependencia quedó resuelta el 2026-08-20: puntos_interes.yaml define las localizaciones de interés de donde salen los orígenes y destinos. NO existe todavía instrumentación, ni una sola corrida registrada, ni conjunto de datos: por eso el avance es del 10 % y no más. La instrumentación se construye junto con la coordinación (S20) y el relevo (S21), no al final, para que las campañas de S24 y S25 solo tengan que ejecutarse. Defecto abierto que hoy sesgaría la tasa de éxito: R12, el verificador de meta cuenta como fallo llegadas que fueron buenas</t>
+          <t>25 %. El protocolo experimental está escrito y versionado desde el 2026-08-22, con las cuatro métricas definidas antes de instrumentar. La instrumentación existe desde el 2026-08-27: esquema de RF-25 versionado y comprobable, grabación de misión sellada con tiempo de simulación y composición del registro validada contra el esquema, con el veredicto calculado contra /odom. Dos misiones de dos tramos grabadas y aprobadas. Falta el analizador de campaña y la condición B, que no puede correr mientras el coordinador no alcance a los dos robots.</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8531,7 @@
       </c>
       <c r="H5" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En ejecución</t>
         </is>
       </c>
     </row>
